--- a/output/stock_quant_scores/GS_income_df.xlsx
+++ b/output/stock_quant_scores/GS_income_df.xlsx
@@ -1129,11 +1129,15 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>60.250001</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>21635000000</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -1151,7 +1155,9 @@
         <v>5488000000</v>
       </c>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>59339000000</v>
+      </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
